--- a/templates/record_template.xlsx
+++ b/templates/record_template.xlsx
@@ -1558,70 +1558,32 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="A5" s="2" t="s"/>
+      <c r="B5" s="2" t="s"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="F5" s="2" t="s"/>
+      <c r="G5" s="2" t="s"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="I5" s="2" t="s"/>
+      <c r="J5" s="2" t="s"/>
       <c r="K5" s="2"/>
-      <c r="L5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="16">
-        <v>1</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>40</v>
-      </c>
+      <c r="L5" s="2" t="s"/>
+      <c r="M5" s="2" t="s"/>
+    </row>
+    <row r="6" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s"/>
+      <c r="B6" s="16" t="s"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16" t="s"/>
       <c r="E6" s="16"/>
-      <c r="F6" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>38</v>
-      </c>
+      <c r="F6" s="16" t="s"/>
+      <c r="G6" s="16" t="s"/>
       <c r="H6" s="16"/>
-      <c r="I6" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>44</v>
-      </c>
+      <c r="I6" s="16" t="s"/>
+      <c r="J6" s="16" t="s"/>
+      <c r="K6" s="16" t="s"/>
       <c r="L6" s="16"/>
       <c r="M6" s="16"/>
     </row>

--- a/templates/record_template.xlsx
+++ b/templates/record_template.xlsx
@@ -1572,20 +1572,20 @@
       <c r="L5" s="2" t="s"/>
       <c r="M5" s="2" t="s"/>
     </row>
-    <row r="6" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s"/>
-      <c r="B6" s="16" t="s"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16" t="s"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16" t="s"/>
-      <c r="G6" s="16" t="s"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16" t="s"/>
-      <c r="J6" s="16" t="s"/>
-      <c r="K6" s="16" t="s"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
+    <row r="6" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s"/>
+      <c r="B6" s="2" t="s"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="s"/>
+      <c r="G6" s="2" t="s"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s"/>
+      <c r="J6" s="2" t="s"/>
+      <c r="K6" s="2" t="s"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
